--- a/data/trans_camb/IQ2606_R2-Habitat-trans_camb.xlsx
+++ b/data/trans_camb/IQ2606_R2-Habitat-trans_camb.xlsx
@@ -519,13 +519,13 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
       <c r="E1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="F1" s="3" t="n"/>
@@ -593,22 +593,22 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>11,03</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>25,03</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
           <t>14,99</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
-        <is>
-          <t>29,7</t>
-        </is>
-      </c>
-      <c r="E4" s="2" t="inlineStr">
-        <is>
-          <t>11,03</t>
-        </is>
-      </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>25,34</t>
+          <t>29,77</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -618,7 +618,7 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>27,41</t>
+          <t>27,29</t>
         </is>
       </c>
     </row>
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>5,32; 24,42</t>
+          <t>1,32; 20,94</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>16,16; 40,44</t>
+          <t>11,05; 36,69</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>1,42; 20,57</t>
+          <t>3,87; 24,1</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>12,49; 36,38</t>
+          <t>15,69; 39,82</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>6,5; 20,16</t>
+          <t>6,45; 19,68</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>18,21; 35,65</t>
+          <t>17,55; 35,31</t>
         </is>
       </c>
     </row>
@@ -669,22 +669,22 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>18,56%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>42,13%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
           <t>26,88%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
-        <is>
-          <t>53,25%</t>
-        </is>
-      </c>
-      <c r="E6" s="2" t="inlineStr">
-        <is>
-          <t>18,56%</t>
-        </is>
-      </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>42,64%</t>
+          <t>53,37%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -694,7 +694,7 @@
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>47,53%</t>
+          <t>47,33%</t>
         </is>
       </c>
     </row>
@@ -707,32 +707,32 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,79; 47,72</t>
+          <t>2,17; 39,39</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>27,94; 80,82</t>
+          <t>19,07; 68,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>2,18; 37,69</t>
+          <t>6,16; 47,85</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,2; 67,22</t>
+          <t>27,23; 79,78</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>10,6; 37,79</t>
+          <t>10,31; 36,1</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>30,25; 65,63</t>
+          <t>30,09; 65,52</t>
         </is>
       </c>
     </row>
@@ -749,22 +749,22 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>15,22</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>33,58</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
           <t>7,76</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>14,29</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>15,22</t>
-        </is>
-      </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>33,75</t>
+          <t>14,43</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -774,7 +774,7 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>25,4</t>
+          <t>25,2</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,46; 14,95</t>
+          <t>8,19; 23,21</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-0,99; 25,68</t>
+          <t>23,93; 41,33</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>7,19; 22,51</t>
+          <t>-1,0; 14,55</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>23,81; 41,38</t>
+          <t>-0,68; 26,02</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>6,31; 16,82</t>
+          <t>6,41; 16,71</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>17,93; 32,3</t>
+          <t>17,18; 32,37</t>
         </is>
       </c>
     </row>
@@ -825,22 +825,22 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>27,88%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>61,51%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
           <t>12,16%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
-        <is>
-          <t>22,41%</t>
-        </is>
-      </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>27,88%</t>
-        </is>
-      </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>61,82%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -850,7 +850,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>43,07%</t>
+          <t>42,74%</t>
         </is>
       </c>
     </row>
@@ -863,32 +863,32 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,65; 25,37</t>
+          <t>13,87; 45,42</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 42,02</t>
+          <t>41,01; 81,38</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>12,72; 45,75</t>
+          <t>-1,28; 24,66</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>41,59; 84,11</t>
+          <t>-0,23; 42,55</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>10,24; 30,34</t>
+          <t>10,48; 29,72</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>29,55; 57,25</t>
+          <t>28,27; 57,16</t>
         </is>
       </c>
     </row>
@@ -905,22 +905,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14,14</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>25,33</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
           <t>13,26</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
-        <is>
-          <t>23,55</t>
-        </is>
-      </c>
-      <c r="E12" s="2" t="inlineStr">
-        <is>
-          <t>14,14</t>
-        </is>
-      </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>24,59</t>
+          <t>22,29</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -930,7 +930,7 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>24,01</t>
+          <t>23,95</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>5,03; 20,97</t>
+          <t>5,58; 21,86</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>11,35; 33,29</t>
+          <t>13,16; 34,37</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>6,21; 22,15</t>
+          <t>5,73; 21,0</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>10,75; 32,85</t>
+          <t>9,27; 31,83</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,01; 19,2</t>
+          <t>7,93; 19,46</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>14,75; 31,33</t>
+          <t>14,99; 30,83</t>
         </is>
       </c>
     </row>
@@ -981,22 +981,22 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>22,2%</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>39,77%</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
           <t>20,23%</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
-        <is>
-          <t>35,92%</t>
-        </is>
-      </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>22,2%</t>
-        </is>
-      </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>34,0%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1006,7 +1006,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>37,17%</t>
+          <t>37,08%</t>
         </is>
       </c>
     </row>
@@ -1019,32 +1019,32 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>7,17; 34,9</t>
+          <t>8,32; 37,73</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>17,22; 55,15</t>
+          <t>20,39; 58,66</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>9,21; 37,71</t>
+          <t>8,13; 34,85</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>17,04; 55,79</t>
+          <t>13,83; 51,84</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>11,82; 31,41</t>
+          <t>11,84; 31,86</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>22,15; 51,48</t>
+          <t>23,19; 50,29</t>
         </is>
       </c>
     </row>
@@ -1061,22 +1061,22 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>21,14</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>25,62</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
           <t>9,46</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
-        <is>
-          <t>21,61</t>
-        </is>
-      </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>21,14</t>
-        </is>
-      </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>26,15</t>
+          <t>19,62</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1086,7 +1086,7 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>23,81</t>
+          <t>22,61</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>0,89; 16,68</t>
+          <t>12,75; 28,57</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>9,71; 31,05</t>
+          <t>10,51; 35,89</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>13,25; 28,95</t>
+          <t>1,22; 17,28</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>12,92; 36,93</t>
+          <t>7,94; 29,17</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>10,14; 21,16</t>
+          <t>9,38; 20,67</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,6; 31,56</t>
+          <t>13,79; 29,95</t>
         </is>
       </c>
     </row>
@@ -1137,22 +1137,22 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>38,69%</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>46,89%</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
           <t>15,2%</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
-        <is>
-          <t>34,71%</t>
-        </is>
-      </c>
-      <c r="E18" s="2" t="inlineStr">
-        <is>
-          <t>38,69%</t>
-        </is>
-      </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>47,85%</t>
+          <t>31,51%</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
@@ -1162,7 +1162,7 @@
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>40,72%</t>
+          <t>38,67%</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>1,38; 28,48</t>
+          <t>20,86; 56,89</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>15,03; 52,56</t>
+          <t>18,84; 70,64</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>22,59; 58,17</t>
+          <t>1,83; 30,54</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>21,78; 71,88</t>
+          <t>13,31; 51,32</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>16,5; 38,56</t>
+          <t>15,49; 37,82</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>24,32; 57,46</t>
+          <t>22,74; 53,69</t>
         </is>
       </c>
     </row>
@@ -1217,22 +1217,22 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>15,81</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
+          <t>28,1</t>
+        </is>
+      </c>
+      <c r="E20" s="2" t="inlineStr">
+        <is>
           <t>10,93</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
-        <is>
-          <t>21,57</t>
-        </is>
-      </c>
-      <c r="E20" s="2" t="inlineStr">
-        <is>
-          <t>15,81</t>
-        </is>
-      </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>28,13</t>
+          <t>20,62</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -1242,7 +1242,7 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>25,06</t>
+          <t>24,6</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>6,74; 15,09</t>
+          <t>12,05; 19,9</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>15,17; 26,66</t>
+          <t>22,41; 32,89</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>11,89; 19,98</t>
+          <t>6,59; 14,91</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>22,44; 33,34</t>
+          <t>14,03; 26,44</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>10,49; 16,29</t>
+          <t>10,45; 16,24</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>21,1; 28,76</t>
+          <t>20,05; 28,52</t>
         </is>
       </c>
     </row>
@@ -1293,22 +1293,22 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>27,47%</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
+          <t>48,81%</t>
+        </is>
+      </c>
+      <c r="E22" s="2" t="inlineStr">
+        <is>
           <t>17,6%</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
-        <is>
-          <t>34,72%</t>
-        </is>
-      </c>
-      <c r="E22" s="2" t="inlineStr">
-        <is>
-          <t>27,47%</t>
-        </is>
-      </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>48,87%</t>
+          <t>33,2%</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -1318,7 +1318,7 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>41,91%</t>
+          <t>41,15%</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>10,32; 25,11</t>
+          <t>20,05; 36,22</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>24,02; 44,05</t>
+          <t>38,09; 59,55</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>19,88; 36,92</t>
+          <t>10,25; 25,34</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>38,02; 59,66</t>
+          <t>22,51; 44,71</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>17,15; 27,92</t>
+          <t>16,96; 27,98</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>34,48; 49,36</t>
+          <t>32,91; 48,94</t>
         </is>
       </c>
     </row>
